--- a/docs/latest.xlsx
+++ b/docs/latest.xlsx
@@ -10,7 +10,7 @@
     <sheet name="국내외단신DB-2026.10" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'국내외단신DB-2026.10'!$B$2:$I$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'국내외단신DB-2026.10'!$B$2:$I$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I66"/>
+  <dimension ref="B2:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -523,28 +523,28 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>파이낸셜뉴스</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>'‘美 원전’도 마스가처럼… 현지인력 키운다</t>
+          <t>원전 공론화서 '노후 원전 계속운전·기존 건설계획' 제외</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://www.fnnews.com/news/202610111830053847</t>
+          <t>https://www.yna.co.kr/view/AKR20261015069900530?input=1195m</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
@@ -557,28 +557,28 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>KBS</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>현대건설, 네덜란드서 신규 원전 사업…대형원전 기본설계 착수</t>
+          <t>산업부 차관에 박동일 산업정책실장…원전·제조업 두루 거친 전문가</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>네덜란드</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261008064600003?input=1195m</t>
+          <t>https://news.kbs.co.kr/news/pc/view/view.do?ncd=8687709&amp;ref=A</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
@@ -591,17 +591,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>문화일보</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>AI發 전력 병목에… 삼성-현대차-포스코, 원전 등 직접 발전 검토</t>
+          <t>코넥서스 CTO “월성 원전 폐쇄 이해못해… 전면 개보수 마쳐 위험성 전혀 없어”</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://www.donga.com/news/Economy/article/all/20261011/134822352/2</t>
+          <t>https://www.munhwa.com/article/11624389?ref=naver</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
@@ -625,28 +625,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>뉴시스</t>
+          <t>문화일보</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>고준위 방폐물 후보부지 내년 공모…연내 부적합지역 배제 마무리</t>
+          <t>(현지 르포) 광역시엔 대형 원전, 산단엔 SMR… ‘청정 캐나다’ 떠받치는 원자력</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>캐나다</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://www.newsis.com/view/NISX20261009_0003820064</t>
+          <t>https://www.munhwa.com/article/11624390?ref=naver</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
@@ -659,17 +659,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>전기신문</t>
+          <t>뉴시스</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>원전 르네상스 왔는데…“일할 사람이 없다” 전문인력 부족에 발목</t>
+          <t>창원시, ‘SMR중심 원전산업’ 미래 50년 먹거리로 육성</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://www.electimes.com/news/articleView.html?idxno=373217</t>
+          <t>https://www.newsis.com/view/NISX20261018_0003830269</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
@@ -693,28 +693,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>이투뉴스</t>
+          <t>에너지안전신문</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>뉴톤-BHI, 10MWe 초소형모듈원자로(MMR) 국내 제작 추진</t>
+          <t>세계 원전 정책의 중심, 인천으로…IAEA 원자력 장관급 회의 27일 개막</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>국제기구</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://www.e2news.com/news/articleView.html?idxno=334972</t>
+          <t>https://www.esnews.kr/news/articleView.html?idxno=6887</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
@@ -727,17 +727,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>신한울 원전에 구동기 공급…"국산 기술로 해외 공략"</t>
+          <t>원자력 창업, 시장과 만나다… '아토믹네스트' 데모데이 개최</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
@@ -748,7 +748,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://www.hankyung.com/article/2026101143981</t>
+          <t>https://view.asiae.co.kr/article/2026101909155839128</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
@@ -756,33 +756,33 @@
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>국내기사</t>
+          <t>세계기사</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>동아사이언스</t>
+          <t>WNN</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>김선민 의원 "원전 8기, 해수온도 제한치까지 2도도 안 남아"</t>
+          <t>슬로바키아 모호우체 4호기, 전력망 최초 연결</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>슬로바키아</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://www.dongascience.com/news/80279</t>
+          <t>https://www.world-nuclear-news.org/articles/mochovce-4-connected-to-the-grid?utm_source=chatgpt.com</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
@@ -790,33 +790,33 @@
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>사설/칼럼/기고</t>
+          <t>세계기사</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>글로벌이코노믹</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>'민간 원전' 논의 시작하자</t>
+          <t>佛 5번째 바라쿠다 원잠 뤼비함 이동… 2030년 전력화 속도</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>프랑스</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/opinion/journalist_view/2026/10/11/ELYY6HSI2FA2DNKDPDITFCMMEU/?utm_source=naver&amp;utm_medium=referral&amp;utm_campaign=naver-news</t>
+          <t>https://www.g-enews.com/view.php?ud=202610181456179516fbbec65dfb_1</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
@@ -824,33 +824,33 @@
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>사설/칼럼/기고</t>
+          <t>세계기사</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>문화일보</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>한국형 원전 APR1400 미국 진출, 원자력의 새로운 장을 열다</t>
+          <t>한국형 핵잠 건조 예산, 특별회계를 만들지 않는 이유는 무엇인가?</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/article/2026100609080281596</t>
+          <t>https://www.munhwa.com/article/11624204?ref=naver</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
@@ -863,28 +863,28 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>투데이에너지</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>中-佛 외교안보 전략대화…"우주·원자력·AI 협력 강화"</t>
+          <t>원전수출시대 한국의 선택</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261011020900083?input=1195m</t>
+          <t>https://www.todayenergy.kr/news/articleView.html?idxno=304315</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
@@ -892,22 +892,22 @@
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>세계기사</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>동아사이언스</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Hyundai E&amp;C tests used fuel repository excavation equipment</t>
+          <t>[인사] 한국원자력연구원</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -918,14 +918,10 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/hyundai-ec-tests-repository-excavation-equipment</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>South Korea's Hyundai Engineering &amp; Construction announced it has employed equipment it has developed to excavate a full-scale deposition hole for used nuclear fuel disposal in the bedrock at its research demonstration site.</t>
-        </is>
-      </c>
+          <t>https://www.dongascience.com/ko/news/80365</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -935,7 +931,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -945,23 +941,23 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Bangladesh's Rooppur 1 achieves criticality</t>
+          <t>Joint venture to produce HALEU in South Africa</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>방글라데시</t>
+          <t>남아프리카공화국</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/bangladeshs-rooppur-1-achieves-criticality</t>
+          <t>https://world-nuclear-news.org/articles/joint-ventureto-produce-haleu-in-south-africa</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>The first unit at Bangladesh's Rooppur Nuclear Power Plant achieved criticality - a self-sustaining nuclear reaction - at 15:34 on Sunday, 11 October.</t>
+          <t>A joint venture between ASP Isotopes Inc subsidiary Quantum Leap Energy and South African state-owned nuclear energy corporation Necsa will develop, finance, build and operate a test bench and commercial-scale facility for the production of high-assay low-enriched uranium at Necsa's Pelindaba site.</t>
         </is>
       </c>
     </row>
@@ -973,7 +969,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -983,7 +979,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>NASA, DOE join forces for 'new era' of space technologies</t>
+          <t>AEP, Amazon and X-energy planning 12-SMR plant</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr"/>
@@ -994,12 +990,12 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/nasa-doe-join-forces-for-new-era-of-space-technologies</t>
+          <t>https://world-nuclear-news.org/articles/aep-amazon-and-x-energy-plan-12-smr-plant</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>The US space and energy agencies have signed a new Memorandum of Understanding establishing a framework for end-to-end collaboration across the full spectrum of space nuclear development.</t>
+          <t>US utility American Electric Power and X-energy have signed a joint development agreement to evaluate a potential 960 MW project at a former coal plant site in Sullivan County, Indiana.</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1007,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1021,7 +1017,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Hanhikivi-1 termination decision cases 'to continue'</t>
+          <t>Rosatom signs floating nuclear power deal for Indonesia</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr"/>
@@ -1032,12 +1028,12 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/hanhikivi-1-termination-decision-cases-to-continue</t>
+          <t>https://world-nuclear-news.org/articles/rosatom-signs-floating-nuclear-power-deal-for-indonesia</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>The project for a 1,200 MWe AES-2006 VVER unit in Finland was terminated by Fennovoima a few weeks after the start of the Russia-Ukraine war.</t>
+          <t>Electricity generated by floating nuclear power plants will be provided to an East Indonesian island, according to an agreement signed by Rosatom and Indonesian company PT Pembangkit Listrik Nuklir.</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1045,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12</t>
+          <t>2026.10.19</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1059,7 +1055,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Milestone for Urenco USA expansion project</t>
+          <t>Oklo plans isotope facility under US Launch Pad initiative</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr"/>
@@ -1070,12 +1066,12 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/milestone-for-urenco-usa-expansion-project</t>
+          <t>https://world-nuclear-news.org/articles/oklo-plans-isotope-facility-under-us-launch-pad-initiative</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>The start of production in the sixth cascade of new uranium enrichment capacity at Urenco USA's National Enrichment Facility in New Mexico means 75% of the ongoing capacity expansion has been completed.</t>
+          <t>Oklo says the Groves-2 Forge isotope production and processing pilot facility will build on the deployment of its Groves Isotope Test Reactor, which reached criticality earlier this year.</t>
         </is>
       </c>
     </row>
@@ -1087,28 +1083,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>이투데이</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>고리 3·4호기 계속운전 심사 시작…사고관리계획서도 동시 심의</t>
+          <t>(2026 국감) 한수원 사장 "SMR·신규 원전 적기 건설⋯체코·이집트 후속 수주 만전"</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>체코</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261012161700017?input=1195m</t>
+          <t>https://www.etoday.co.kr/news/view/2637439</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
@@ -1121,17 +1117,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>에너지데일리</t>
+          <t>전기신문</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>(2026 국감) 반도체 전력망·해외 원전사업 도마…산자중기위, 한전·한수원 집중 점검</t>
+          <t>(2026 국감) 원전 건설비 14.5조↑…공론화서 따질 ‘진짜 비용’은?</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr"/>
@@ -1142,7 +1138,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://www.energydaily.co.kr/news/articleView.html?idxno=203974</t>
+          <t>https://www.electimes.com/news/articleView.html?idxno=373637</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
@@ -1155,17 +1151,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>인사이트N파워</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>(2026 국감) 한전 사장 "웨스팅하우스 로열티 20억달러는 상한 가이드라인"</t>
+          <t>(2026 국감) 원전 핵심구역 출입기록 ‘서명 면제’ 오인이 부른 관리 허점</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
@@ -1176,7 +1172,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261012091700003?input=1195m</t>
+          <t>https://www.inpnews.kr/news/articleView.html?idxno=8044</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
@@ -1189,17 +1185,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>부산일보</t>
+          <t>에너지타임뉴스</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>(2026 국감) “한빛·한울원전 사용후핵연료 포화 시점, 건식시설 가동 목표와 겹쳐”</t>
+          <t>OECD/NEA 핵연료 국제공동연구 FIDES 정기회의 대전서 개최</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
@@ -1210,7 +1206,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://www.busan.com/view/busan/view.php?code=2026101217265740139</t>
+          <t>https://www.enertopianews.co.kr/news/articleView.html?idxno=60445</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr"/>
@@ -1223,17 +1219,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>쿠키뉴스</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>해수부, 런던의정서 당사국총회 참석…원전오염수 안전관리 강조</t>
+          <t>비슷한 듯 다른 SK그룹-HD현대의 원전 셈법, 최종 목표는</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
@@ -1244,7 +1240,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261012019600051?input=1195m</t>
+          <t>https://www.kukinews.com/article/view/kuk202610190218</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
@@ -1257,28 +1253,28 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>파이낸셜뉴스</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>가온전선, 美 원전용 케이블 생산설비 구축 나선다</t>
+          <t>우주선·원자로 부품 '숨은 손상' 찾는다</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://biz.heraldcorp.com/article/10899217?ref=naver</t>
+          <t>https://www.fnnews.com/news/202610191340377998</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr"/>
@@ -1286,22 +1282,22 @@
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>사설/칼럼/기고</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>전기신문</t>
+          <t>영남일보</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>내일의 원자력, 오늘부터 규제를 준비해야 한다</t>
+          <t>새 원전이 주는 새 희망…영덕 신규원전의 첫걸음</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
@@ -1312,7 +1308,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>https://www.electimes.com/news/articleView.html?idxno=373281</t>
+          <t>https://www.yeongnam.com/web/view.php?key=20261019020542027</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
@@ -1320,22 +1316,22 @@
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>사설/칼럼/기고</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>경북일보</t>
+          <t>인사이트N파워</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>탄소중립 관건 수소환원제철, 원전 없이 어렵다</t>
+          <t>김병구 前 원자력硏 단장, 신간 『다시, 원자력을 묻는 시간』 출간</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr"/>
@@ -1346,7 +1342,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>https://www.kyongbuk.co.kr/news/articleView.html?idxno=4086870</t>
+          <t>https://www.inpnews.kr/news/articleView.html?idxno=8052</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr"/>
@@ -1354,104 +1350,112 @@
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>사설/칼럼/기고</t>
+          <t>WNN</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>부산일보</t>
+          <t>World Nuclear News</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>일정 빠듯한 사용후핵연료 처리 로드맵, 종합 대책 필요</t>
+          <t>Philippines advances plans for nuclear power as energy demand rises</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>필리핀</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>https://mobile.busan.com/view/election/view.php?code=2026101218060263648</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr"/>
+          <t>https://world-nuclear-news.org/articles/philippines-advances-plans-for-nuclear-power-as-energy-demand-rises</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>The Philippines is working to establish the policy, regulatory and commercial foundations for its first nuclear power project, with a target of 1.2 GW of capacity by 2032 and a longer-term ambition to reach 4.8 GW by 2050, the World Nuclear Supply Chain conference in Manila heard.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>세계기사</t>
+          <t>WNN</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>에너지안전신문</t>
+          <t>World Nuclear News</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>방글라데시, 러시아 손잡고 '원자력 시대' 점화…루푸르 1호기 임계 돌파</t>
+          <t>Aura aims for final investment decision on Mauritania project this year</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>러시아</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>https://www.esnews.kr/news/articleView.html?idxno=6757</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr"/>
+          <t>https://world-nuclear-news.org/articles/aura-aims-fid-mauritania-project-this-year</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Aura Energy Limited says it is targeting a final investment decision by the end of the year for the Tiris uranium project in Mauritania as a newly released bankable feasibility study confirms the project's economics. But Deep Yellow says current equity market conditions don't support a final investment decision for its Tumas project in Namibia during the current quarter.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>세계기사</t>
+          <t>WNN</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>에너지안전신문</t>
+          <t>World Nuclear News</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>아르메니아, 원전 2036년까지 쓴다…계속운전 위한 설비개선 확대</t>
+          <t>Indiana considering 6 GW Candu nuclear project</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>아르메니아</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>https://www.esnews.kr/news/articleView.html?idxno=6756</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr"/>
+          <t>https://world-nuclear-news.org/articles/indiana-considering-6-gw-candu-nuclear-project</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>AtkinsRéalis Group, Hoosier Energy Rural Electric Cooperative and the State of Indiana in the US are to explore a potential project featuring up to eight Candu nuclear power units, with a combined 6 GW capacity.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
@@ -1461,7 +1465,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1471,177 +1475,161 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Agreement signed on second Polish nuclear power plant</t>
+          <t>Korean concern over proposed 'Made in EU' act's impact on nuclear power projects</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>폴란드</t>
+          <t>체코</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/agreement-signed-on-second-polish-nuclear-power-plant</t>
+          <t>https://world-nuclear-news.org/articles/korean-concerns-over-proposed-made-in-eu-acts-impact-nuclear-power-projects</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Poland's Ministry of Energy, Polskie Elektrownie Jądrowe and Polska Grupa Energetyczna have signed an agreement defining the division of tasks and principles of cooperation in preparing the construction of the country's second nuclear power plant.</t>
+          <t>Progress on the Dukovany new nuclear project is continuing on schedule, but South Korea has concerns about the potential impact of the European Union's proposed Industrial Accelerator Act on non-member countries participating in the EU's nuclear power market.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>NND applies to take over Kjeller nuclear facilities</t>
+          <t>한-체코, 두코바니 원전 점검…EU 산업가속화법 대응 논의</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>노르웨이</t>
+          <t>체코</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/nnd-applies-to-take-over-kjeller-nuclear-facilities</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>Norwegian Nuclear Decommissioning has submitted a licence application to the country's nuclear regulator to take over responsibility for the nuclear facilities at Kjeller from the Institute of Energy Engineering ahead of their decommissioning.</t>
-        </is>
-      </c>
+          <t>https://www.yna.co.kr/view/AKR20261020045500003?input=1195m</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>뉴시스</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Czech SMR environmental impact assessment submitted</t>
+          <t>한울원전 1호기 발전 정지, 계획예방정비에 착수</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>영국</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/czech-smr-environmental-impact-assessment-submitted</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>ČEZ has submitted the Environmental Impact Assessment documentation to the Ministry of the Environment for its Rolls-Royce SMR small modular reactor project in Temelín.</t>
-        </is>
-      </c>
+          <t>https://www.newsis.com/view/NISX20261020_0003833108</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>쿠키뉴스</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Agreement aims to support US maritime nuclear</t>
+          <t>(2026 국감) 원자력연 특허 480건 ‘미활용’…4건 중 1건은 10년 넘게 방치</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/agreements-and-deals-support-us-maritime-nuclear-developments</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>The American Bureau of Shipping and the US Department of Energy have signed a memorandum of understanding to advance modern commercial nuclear technology at sea.</t>
-        </is>
-      </c>
+          <t>https://www.kukinews.com/article/view/kuk202610200061</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>IAEA carries out fresh LTO review mission to Oskarshamn</t>
+          <t>AI 붐에 주목받는 '소형 원전(SMR)'…국내 스타트업은 틈새 공급망 공략</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>스웨덴</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/iaea-carries-out-fresh-lto-review-mission-to-oskarshamn</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>The International Atomic Energy Agency team focused on aspects related to the safe Long Term Operation of Sweden's Oskarshamn 3 nuclear power unit during the visit, which followed a similar mission two years earlier.</t>
-        </is>
-      </c>
+          <t>https://www.chosun.com/economy/tech_it/2026/10/20/QBCC7LPKENDXJAKLBLKR6V6Y2I/?utm_source=naver&amp;utm_medium=referral&amp;utm_campaign=naver-news</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="2" t="inlineStr">
@@ -1651,17 +1639,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>동아사이언스</t>
+          <t>뉴시스</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>원자력안전위원회 2027년 상반기 세종 이전…출범 15년만</t>
+          <t>원전 소재 5개 지자체 "사용후핵연료 저장시설 지원을"</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr"/>
@@ -1672,7 +1660,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://www.dongascience.com/news/80313</t>
+          <t>https://www.newsis.com/view/NISX20261020_0003834004</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr"/>
@@ -1685,17 +1673,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>뉴스1</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>SMR 인허가 전 '사전검토' 11월 시행…원안위, 규제체계 정비</t>
+          <t>우진엔텍, 고리 3·4호기 정비용역 51억 증액…“계속운전 설비개선 반영”</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr"/>
@@ -1706,7 +1694,7 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://www.news1.kr/it-science/general-science/6317989</t>
+          <t>https://www.mk.co.kr/news/stock/12181358</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr"/>
@@ -1719,28 +1707,28 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>[2026 국감] 방사선 피폭사고 뒤에도 안전 위반…원전 사고관리계획서 7년째 표류</t>
+          <t>지투파워, 체코·슬로바키아 원전 기자재 기업 3곳과 MOU…"유럽 시장 공략"</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>체코</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/article/enterprise-CEO/2026101318180032430</t>
+          <t>https://www.edaily.co.kr/News/Read?newsId=03001206645614888&amp;mediaCodeNo=257&amp;utm_source=naver&amp;utm_medium=referral&amp;utm_campaign=news_syndication&amp;utm_content=original_article</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr"/>
@@ -1753,17 +1741,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>뉴시스</t>
+          <t>동아일보</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>[2026 국감] 원안위원장 "고리 3·4호기 계속운전, 이달 중 심의…안전성 철저히 확인"</t>
+          <t>손으로 대조하던 원전 서류…AI 들이자 검토 시간 90%↓</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr"/>
@@ -1774,7 +1762,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://www.newsis.com/view/NISX20261013_0003823515</t>
+          <t>https://www.donga.com/news/It/article/all/20261020/134873224/2</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr"/>
@@ -1787,17 +1775,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>에너지안전신문</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>[2026 국감]"4253억 원자력기금, 7년간 결재 문서 없다"…원전 안전관리 도마 위</t>
+          <t>세계 SMR 강자 제주 집결…차세대 원자로 상용화 주도권 경쟁</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr"/>
@@ -1808,7 +1796,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://view.asiae.co.kr/article/2026101315521626074</t>
+          <t>https://www.esnews.kr/news/articleView.html?idxno=6934</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
@@ -1821,17 +1809,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>에너지데일리</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>원자력연, SMR 가속화 전문가 심포지엄 개최</t>
+          <t>글로벌 원전 공급망 협력의 장 'NES 2026', 경주서 열린다</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr"/>
@@ -1842,7 +1830,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://www.sedaily.com/article/20100888?ref=naver</t>
+          <t>https://www.energydaily.co.kr/news/articleView.html?idxno=204226</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr"/>
@@ -1855,17 +1843,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>매일신문</t>
+          <t>에너지안전신문</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>"SMR 경쟁력, 만드는 능력에 달렸다"…국립창원대서 원자력 정책 세미나</t>
+          <t>원자력산업협회 창립 54주년 … 원전 불모지서 ‘560개 기업 회원사' 이룩</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr"/>
@@ -1876,7 +1864,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://www.imaeil.com/page/view/2026101409082093224</t>
+          <t>https://www.esnews.kr/news/articleView.html?idxno=6821</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr"/>
@@ -1884,22 +1872,22 @@
     <row r="42">
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>국내기사</t>
+          <t>사설/칼럼/기고</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>충남일보</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>'내가 만난 원자력' 이야기를 들려줘</t>
+          <t>원전 공론화, 탈진영 계기로</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr"/>
@@ -1910,7 +1898,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://www.chungnamilbo.co.kr/news/articleView.html?idxno=914500</t>
+          <t>https://www.mk.co.kr/news/contributors/12180837</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
@@ -1923,17 +1911,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>경북일보</t>
+          <t>문화일보</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>고준위 방폐물 처분장 건설 미뤄선 안 돼</t>
+          <t>다음단계 도약하는 韓원자력… 국제사회 파트너 자리매김</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr"/>
@@ -1944,7 +1932,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://www.kyongbuk.co.kr/news/articleView.html?idxno=4087028</t>
+          <t>https://www.munhwa.com/article/11624830</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr"/>
@@ -1952,33 +1940,33 @@
     <row r="44">
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>세계기사</t>
+          <t>사설/칼럼/기고</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>에너지안전신문</t>
+          <t>이뉴스투데이</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>원전, 건설비만 따지면 오판…IAEA가 짚은 ‘진짜 비용’</t>
+          <t>원자력 PPA, 설계의 문제다</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>국제기구</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://www.esnews.kr/news/articleView.html?idxno=6774</t>
+          <t>https://www.enewstoday.co.kr/news/articleView.html?idxno=2482227</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr"/>
@@ -1986,40 +1974,32 @@
     <row r="45">
       <c r="B45" s="2" t="inlineStr">
         <is>
+          <t>세계기사</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2026.10.21</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
           <t>WNN</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>2026.10.14</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>World Nuclear News</t>
-        </is>
-      </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Westinghouse places initial orders for Polish plant</t>
+          <t>JAIF “원전 1기 교체 건설 시 경제 파급효과 4조3000억엔</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>미국</t>
-        </is>
-      </c>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/westinghouse-places-initial-orders-for-polish-plant</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>Westinghouse has placed conditional purchase orders for safety-related modules with four Polish companies, a week after being commissioned to begin ordering long-lead items for the first unit of Poland's planned first nuclear power plant.</t>
-        </is>
-      </c>
+          <t>https://world-nuclear-news.org/articles/jaif-estimates-economic-impact-from-nuclear-power-plants</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="2" t="inlineStr">
@@ -2029,7 +2009,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2039,19 +2019,19 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Namibia takes step towards nuclear power</t>
+          <t>ASEAN nations assessing nuclear energy option</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/namibia-takes-step-towards-nuclear-power</t>
+          <t>https://world-nuclear-news.org/articles/asean-nations-assessing-nuclear-energy-option</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Namibia's Prime Minister has appointed a Nuclear Commissioner to coordinate preparations for nuclear energy and put in place a structure to provide high-level policy coordination and strategic oversight.</t>
+          <t>Southeast Asian countries are taking a pragmatic look at nuclear power as they seek to meet rapidly growing electricity demand, strengthen energy security and diversify their power generation mix, delegates heard at the World Nuclear Supply Chain conference in Manila.</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2043,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2073,23 +2053,23 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Kairos Power automates fuel pebble inspections</t>
+          <t>Westinghouse invests USD1 billion in US LEU+ fuel plant</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>멕시코</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/kairos-power-automates-fuel-pebble-inspections</t>
+          <t>https://world-nuclear-news.org/articles/westinghouse-invests-usd1-billion-in-us-leu-fuel-plant</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>A new facility at Kairos Power's Manufacturing Development Campus in Albuquerque, New Mexico, verifies manufacturing specifications and engraves each fuel pebble with a unique code so it can be traced through testing and operation.</t>
+          <t>Westinghouse has announced a USD1 billion investment in the first new fleet-scale nuclear fuel factory to be built in the USA in more than 50 years, at the Columbia Fuel Fabrication Facility in Hopkins, South Carolina.</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2081,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2111,7 +2091,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>US maritime nuclear firm Bluecore Energy announces uranium purchase</t>
+          <t>The Nuclear Company proposes 6.6 GW Kentucky project</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr"/>
@@ -2122,12 +2102,12 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/us-maritime-nuclear-firm-bluecore-energy-announces-uranium-purchase</t>
+          <t>https://world-nuclear-news.org/articles/nuclear-company-proposes-66-gw-kentucky-project</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>California-based Bluecore Energy said its purchase of low-enriched uranium from WMC is one of several areas where it has made "significant progress" towards moving its technology from engineering and non-fuelled hardware development toward fuel fabrication, testing, validation and future deployment.</t>
+          <t>The Nuclear Company has outlined plans for an energy campus in Lewis County, Kentucky, which could feature up to six AP1000 reactors - this would make its 6.6 GW capacity larger than any current nuclear power plant in the USA.</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2119,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2026.10.14</t>
+          <t>2026.10.21</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2149,23 +2129,23 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Hot testing of Chinese SMR under way</t>
+          <t>IAEA says Barakah drone-strike response was effective</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/hot-testing-of-chinese-smr-under-way</t>
+          <t>https://world-nuclear-news.org/articles/iaea-says-barakah-drone-strike-response-was-effective</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Tests that simulate the temperatures and pressures which the reactor systems will be subjected to during normal operation are reportedly taking place at the ACP100 small modular reactor demonstration project, under construction at the Changjiang site on China's island province of Hainan.</t>
+          <t>An International Atomic Energy Agency mission to the United Arab Emirates has said that effective action was taken following the loss of off-site power to Barakah Nuclear Power Plant's unit 3 following a drone strike in May which caused a fire in a generator located outside the inner perimeter of the plant.</t>
         </is>
       </c>
     </row>
@@ -2177,17 +2157,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.22</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>국제신문</t>
+          <t>매일신문</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>이진호 원자력환경공단 이사장 취임…"고준위 방폐물 부지선정 총력"</t>
+          <t>11월 1일 멈춰서는 월성원전 2호기…늦어지는 계속운전</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr"/>
@@ -2198,7 +2178,7 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://www.kookje.co.kr/news2011/asp/newsbody.asp?code=00&amp;key=20261014.99099004012</t>
+          <t>https://www.imaeil.com/page/view/2026101522490658128</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr"/>
@@ -2211,17 +2191,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.22</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>뉴시스</t>
+          <t>M이코노미뉴스</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>오늘 '고리 3·4호기' 계속운전 심사 개시…승인 시 3개월 후 상업 운전</t>
+          <t>원전 사이버보안 규제인력 19% 감소…3년 연속 증원 승인 ‘0명’</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr"/>
@@ -2232,7 +2212,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://www.newsis.com/view/NISX20261014_0003826017</t>
+          <t>https://www.m-economynews.com/news/article.html?no=71964</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr"/>
@@ -2245,17 +2225,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.22</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>뉴시스</t>
+          <t>인사이트N파워</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>원자로 냉각재 유출된다면…고리2호기 첫 사고관리 훈련</t>
+          <t>최성민 원자력학회장 “원전산업의 미래, 결국 사람과 리더십에 달렸다”</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr"/>
@@ -2266,7 +2246,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://www.newsis.com/view/NISX20261014_0003826152</t>
+          <t>https://www.inpnews.kr/news/articleView.html?idxno=8062</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr"/>
@@ -2279,17 +2259,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.22</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>인사이트N파워</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>한빛 1호기, '한수원 손실' 줄이려 계획보다 27일 더 가동</t>
+          <t>장문희 서울대 연구위원,『원자력: 인간의 삶에서 AI시대까지』출간</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr"/>
@@ -2300,7 +2280,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://www.yna.co.kr/view/AKR20261014027900530?input=1195m</t>
+          <t>https://www.inpnews.kr/news/articleView.html?idxno=8031</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr"/>
@@ -2308,22 +2288,22 @@
     <row r="54">
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>국내기사</t>
+          <t>사설/칼럼/기고</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.22</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>한겨레</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>SMR 엔지니어링 스타트업 알엑스, 프리A 브리지 100억 투자 유치</t>
+          <t>원전 전력구매계약 특혜 논란…공평한 제도 설계 출발점 삼자</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr"/>
@@ -2334,7 +2314,7 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://www.hankyung.com/article/202610140384r</t>
+          <t>https://www.hani.co.kr/arti/opinion/because/1283536.html</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr"/>
@@ -2342,33 +2322,29 @@
     <row r="55">
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>국내기사</t>
+          <t>세계기사</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.22</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>에너지뉴스</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>세아베스틸, BWXT 캐나다와 원전 고부가 기자재 공급 협력 모색</t>
+          <t>홀텍, 팰리세이즈 원전 기울어진 핵연료 집합체 인양 성공</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>캐나다</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://www.edaily.co.kr/News/Read?newsId=02896246645613248&amp;mediaCodeNo=257&amp;utm_source=naver&amp;utm_medium=referral&amp;utm_campaign=news_syndication&amp;utm_content=original_article</t>
+          <t>https://www.2news.co.kr/news/articleView.html?idxno=29964</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr"/>
@@ -2376,70 +2352,78 @@
     <row r="56">
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>국내기사</t>
+          <t>WNN</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.22</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>World Nuclear News</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>"UST, 원전 해체용 제염 공정 개발… 독성 약품 줄이고 폐액 처리</t>
+          <t>OPG firm joins UK BWRX-300 project</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>영국</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/science-chosun/science/2026/10/14/XI2M2SSR2BARPHD7FATOU464R4/?utm_source=naver&amp;utm_medium=original&amp;utm_campaign=biz</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr"/>
+          <t>https://world-nuclear-news.org/articles/joint-venture-to-operate-planned-uk-bwrx-300-fleet</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>The UK-based project company of European SMR developer and investor SGE, and Origin Nuclear, a subsidiary of Ontario Power Generation, have signed a letter of intent to establish a joint venture for the future operation of a planned fleet of 14 BWRX-300 small modular reactors.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>세계기사</t>
+          <t>WNN</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.22</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>글로벌이코노믹</t>
+          <t>World Nuclear News</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>석탄화력 끄고 원전 켜는 폴란드, 제2원전 밑그림 그렸다</t>
+          <t>Radiant microreactor selected for deployment by US Navy</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>폴란드</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/article/Global-Biz/2026/10/202610141112585117fbbec65dfb_1</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr"/>
+          <t>https://world-nuclear-news.org/articles/radiant-microreactor-selected-for-deployment-by-us-navy</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>The US Navy has selected Radiant's Kaleidos microreactor for deployment at Naval Weapons Station Crane, Indiana.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="B58" s="2" t="inlineStr">
@@ -2449,7 +2433,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.22</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2459,332 +2443,520 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>MHI delivers replacement steam generators for French reactor</t>
+          <t>SMRs could be part of Port of Rotterdam's future, says study</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>일본</t>
+          <t>네덜란드</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/mhi-delivers-replacement-steam-generators-for-french-reactor</t>
+          <t>https://world-nuclear-news.org/articles/smrs-could-be-part-of-port-of-rotterdams-future-says-study</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Japan's Mitsubishi Heavy Industries has delivered a further three replacement steam generators to EDF. They are scheduled to be installed in unit 2 of its Cruas nuclear power plant in southeastern France.</t>
+          <t>The Dutch port of Rotterdam could become part of the future small modular reactor supply chain - with opportunities extending well beyond the adoption of nuclear technology itself, according to a study conducted jointly by Tractebel and Technopolis Group.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.23</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Milestone for Bruce 4 refurbishment</t>
+          <t>12월 11부터 사흘간 ‘원전 공론화’…전문가 위원 9인 선정</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>캐나다</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/milestone-for-bruce-4-refurbishment</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>Installation of the unit's 480 calandria tubes was completed faster than at Bruce 3 as the team carrying out the Major Component Replacement project continues to set new records for CANDU refurbishment.</t>
-        </is>
-      </c>
+          <t>https://www.sedaily.com/article/20104888?ref=naver</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.23</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>뉴시스</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>US DOE funding to accelerate molten salt reactor development</t>
+          <t>SMR·양자·우주 찍었다… 정부, '7대 SEED 프로젝트' 연내 세부 로드맵 완성</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/us-doe-funding-to-accelerate-molten-chloride-reactor-development</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>The Molten Chloride Reactor Experiment aims to achieve first criticality in 2027, with the US Department of Energy approving cost-shared funding under its Advanced Reactor Demonstration Program.</t>
-        </is>
-      </c>
+          <t>https://www.newsis.com/view/NISX20261022_0003836178</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.23</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>머니투데이</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Joint venture formed for six-unit SMR plant in Poland</t>
+          <t>(2026 국감) 산업부 장관 "산업과 에너지 같이 가야…원전 정책 이원화는 비효율"</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>폴란드</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/joint-venture-formed-for-six-unit-smr-plant-in-poland</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>Poland's SGE and ZE Pak have agreed to establish a joint venture to develop a nuclear power plant in Pątnów which will feature up to six BWRX-300 small modular reactors.</t>
-        </is>
-      </c>
+          <t>https://www.mt.co.kr/economy/2026/10/22/2026102210554020799</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2026.10.15</t>
+          <t>2026.10.23</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Newcleo opens MOX fuel development centre</t>
+          <t>한미 원전 협력 물꼬 트이자…한수원, APR 운용사 모임 법인화 추진</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>프랑스</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/newcleo-opens-mox-fuel-development-centre</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>Innovative nuclear energy company Newcleo has inaugurated its EUR10 million (USD11 million) advanced nuclear fuel engineering, testing and training centre located in Chusclan, in the Gard department in southern France.</t>
-        </is>
-      </c>
+          <t>https://biz.chosun.com/industry/company/2026/10/22/7BNDFBHEFNDRXHNF4QUUYJQGCY/?utm_source=naver&amp;utm_medium=original&amp;utm_campaign=biz</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2026.10.16</t>
+          <t>2026.10.23</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>에너지신문</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Multiple milestones for India's nuclear projects</t>
+          <t>방폐물 관리에 들어온 AI...성능보다 ‘신뢰성’이 먼저</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>인도</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/multiple-milestones-for-indias-nuclear-projects</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>Technical studies have begun onsite for Kakrapar units 5 and 6, two 700 MWe reactors planned for construction in Gujarat; India's Nuclear Fuels Complex is making steam generator tubes to support the fleet mode construction project; and India's small modular reactor project has reached a design milestone.</t>
-        </is>
-      </c>
+          <t>https://www.energy-news.co.kr/news/articleView.html?idxno=229179</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2026.10.16</t>
+          <t>2026.10.23</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>한국일보</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Mochovce 4 connected to the grid</t>
+          <t>원전·청정수소·영농태양광 'CFE 믹스'… "울진, 무탄소 에너지 특화 도시로"</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>슬로바키아</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/mochovce-4-connected-to-the-grid</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>Slovakia's newest nuclear power unit, Mochovce 4, has been connected and started supplying its first electricity to the grid.</t>
-        </is>
-      </c>
+          <t>https://www.hankookilbo.com/news/article/A2026102117550001143</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>국내기사</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2026.10.16</t>
+          <t>2026.10.23</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>경북매일</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Norwegian used fuel to be stored in Sweden</t>
+          <t>2026 경북원자력포럼 “AI 시대, 경북 원자력이 대한민국 미래 산업 밝힌다”</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>스웨덴</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/norwegian-used-fuel-to-be-stored-in-sweden</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>Norwegian Nuclear Decommissioning has signed an agreement with Swedish nuclear technical services provider Studsvik to manage used nuclear fuel from the former research reactors at Halden and Kjeller.</t>
-        </is>
-      </c>
+          <t>https://www.kbmaeil.com/article/20261022500729</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>WNN</t>
+          <t>세계기사</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2026.10.16</t>
+          <t>2026.10.23</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>World Nuclear News</t>
+          <t>에너지안전신문</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Thorizon, TNO launch MSR materials programme</t>
+          <t>대만, 65년 연구용 원자로 교체 시동…국립칭화대·美 뉴큐브 MMR 협력</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>네덜란드</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/thorizon-tno-launch-msr-materials-programme</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>Molten salt reactor developer Thorizon and Dutch research and technology organisation TNO have launched a materials and corrosion programme to generate the experimental data and predictive models required to qualify materials for molten salt reactors.</t>
+          <t>https://www.esnews.kr/news/articleView.html?idxno=6956</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>세계기사</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>2026.10.23</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>연합뉴스</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>푸틴, 中총리와 회담…"에너지·원자력·AI·교통운수 협력하자"</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.yna.co.kr/view/AKR20261022000651109?input=1195m</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>세계기사</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2026.10.23</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>헝가리, 팍스 원전 사업서 러시아 로사톰 교체 검토</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>러시아</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.g-enews.com/article/Global-Biz/2026/10/2026102214023771602bd56fbc3c_1</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>WNN</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>2026.10.23</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>World Nuclear News</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Posiva given go-ahead to operate Finnish used fuel repository</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>핀란드</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>https://world-nuclear-news.org/articles/posiva-given-go-ahead-to-operate-finnish-used-fuel-repository</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Finnish radioactive waste management company Posiva has been granted a licence to operate the encapsulation and final disposal facility for used nuclear fuel located in Olkiluoto. It is the world's first repository for used fuel to be granted such a licence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>WNN</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>2026.10.23</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>World Nuclear News</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>FID sees Etango enter full-scale construction</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>https://world-nuclear-news.org/articles/fid-sees-etango-enter-full-scale-construction</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>A positive final investment decision from the Bannerman Energy-CNNC Overseas joint venture means the Etango uranium project in Namibia can transition into full-scale construction activities, with commissioning and production targeted for 2028.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>WNN</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>2026.10.23</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>World Nuclear News</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Rosatom eyes 2027 for Uzbek large reactor construction</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>러시아</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>https://world-nuclear-news.org/articles/rosatom-eyes-2027-for-uzbek-reactor-construction</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Rosatom plans to launch construction of the large-scale nuclear units at the planned power plant in Uzbekistan in 2027, CEO Alexey Likhachev has said during a visit to the construction site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>WNN</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>2026.10.23</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>World Nuclear News</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Slovenia's deep borehole disposal options studied</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>https://world-nuclear-news.org/articles/slovenias-deep-borehole-disposal-options-studied</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>The US firm Deep Isolation has conducted a cost assessment for Slovenia's radioactive waste agency which has concluded it would be more economic for used fuel from the TRIGA II research reactor and from the Krško Nuclear Power Plant to be placed in the same disposal facility deep underground.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:I66"/>
+  <autoFilter ref="B2:I72"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
@@ -2850,6 +3022,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
